--- a/testdata/HotelNames.xlsx
+++ b/testdata/HotelNames.xlsx
@@ -12,7 +12,61 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>Hob House</t>
+  </si>
+  <si>
+    <t>Kingfisher Nest Hotel Suites</t>
+  </si>
+  <si>
+    <t>Cloud Hotel &amp; Suites</t>
+  </si>
+  <si>
+    <t>Hotel Troy Nairobi</t>
+  </si>
+  <si>
+    <t>Diamond Plaza Apartments</t>
+  </si>
+  <si>
+    <t>Mövenpick Hotel &amp; Residences Nairobi</t>
+  </si>
+  <si>
+    <t>Holiday Inn Nairobi Two Rivers Mall by IHG</t>
+  </si>
+  <si>
+    <t>Acacia Tree Lodge</t>
+  </si>
+  <si>
+    <t>Karen Gables</t>
+  </si>
+  <si>
+    <t>Crowne Plaza Nairobi Airport by IHG</t>
+  </si>
+  <si>
+    <t>Hotel Boulevard Nairobi, City Centre CBD</t>
+  </si>
+  <si>
+    <t>Best Western Premier Westlands</t>
+  </si>
+  <si>
+    <t>Best Western Plus Meridian Hotel</t>
+  </si>
+  <si>
+    <t>The Heron By Sarovar Portico India</t>
+  </si>
+  <si>
+    <t>Ibis Styles Nairobi Westlands</t>
+  </si>
+  <si>
+    <t>Four Points By Sheraton Nairobi Airport</t>
+  </si>
+  <si>
+    <t>PrideInn Azure Hotel Nairobi Westlands</t>
+  </si>
+  <si>
+    <t>Villa Rosa Kempinski</t>
+  </si>
   <si>
     <t>The Boma Nairobi</t>
   </si>
@@ -20,88 +74,40 @@
     <t>Boma Inn Nairobi</t>
   </si>
   <si>
+    <t>Mercure Nairobi Upper Hill</t>
+  </si>
+  <si>
+    <t>Tribe Hotel</t>
+  </si>
+  <si>
+    <t>Longonot Place Serviced Apartments- Nairobi, City Centre CBD</t>
+  </si>
+  <si>
+    <t>Villa Leone</t>
+  </si>
+  <si>
+    <t>Highlands Suites Apartment Hotel</t>
+  </si>
+  <si>
+    <t>Sarova Stanley Hotel, Nairobi</t>
+  </si>
+  <si>
+    <t>Nairobi Serena Hotel</t>
+  </si>
+  <si>
     <t>Tamarind Tree Hotel</t>
   </si>
   <si>
-    <t>Hotel Rio</t>
-  </si>
-  <si>
-    <t>Eka Hotel Nairobi</t>
-  </si>
-  <si>
-    <t>Alina Ridge Wonders Apartments</t>
-  </si>
-  <si>
-    <t>Qusini Kenya</t>
-  </si>
-  <si>
-    <t>Lux Suites Enzi Heights Apartments</t>
-  </si>
-  <si>
-    <t>Cozy Studio Apartment - Nairobi West</t>
-  </si>
-  <si>
-    <t>Arova Hotel</t>
-  </si>
-  <si>
-    <t>Argyle Grand Hotel Nairobi Airport</t>
-  </si>
-  <si>
-    <t>Nairobi West Suites</t>
-  </si>
-  <si>
-    <t>Aero Club of East Africa</t>
-  </si>
-  <si>
-    <t>Red Buffalo House Hotel</t>
-  </si>
-  <si>
-    <t>The Curve by the Park Apartments</t>
-  </si>
-  <si>
-    <t>Emara Ole-sereni</t>
-  </si>
-  <si>
-    <t>The Stand Leisure Hotel</t>
-  </si>
-  <si>
-    <t>Hanan Guest House</t>
-  </si>
-  <si>
-    <t>Weston Hotel</t>
-  </si>
-  <si>
-    <t>Mercure Nairobi Upper Hill</t>
-  </si>
-  <si>
-    <t>Melili Hotel</t>
-  </si>
-  <si>
-    <t>Kozi Wilson Airport</t>
-  </si>
-  <si>
-    <t>Lux Suites Wawazi Court Apartments</t>
-  </si>
-  <si>
-    <t>The Attic Place South B</t>
-  </si>
-  <si>
-    <t>Lux Suites Laurel Hill Suites</t>
-  </si>
-  <si>
-    <t>Almaj Galaxie Hotel</t>
-  </si>
-  <si>
-    <t>Lux Suites Oak South Gardens Apartments</t>
-  </si>
-  <si>
-    <t>Sagwe Furnished Apartments</t>
-  </si>
-  <si>
-    <t>Liberty Gardens Apartments South B</t>
-  </si>
-  <si>
-    <t>Lux Suites Attic Place Studio Apartemnts</t>
+    <t>Yaya Hotel and Apartments</t>
+  </si>
+  <si>
+    <t>Fairmont The Norfolk</t>
+  </si>
+  <si>
+    <t>Bidwood Suite Hotel</t>
+  </si>
+  <si>
+    <t>Executive Residency by Best Western Nairobi</t>
   </si>
 </sst>
 </file>
@@ -146,7 +152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -299,6 +305,16 @@
         <v>29</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/testdata/HotelNames.xlsx
+++ b/testdata/HotelNames.xlsx
@@ -14,21 +14,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
+    <t>Kingfisher Nest Hotel Suites</t>
+  </si>
+  <si>
+    <t>Cloud Hotel &amp; Suites</t>
+  </si>
+  <si>
+    <t>Hotel Troy Nairobi</t>
+  </si>
+  <si>
+    <t>Diamond Plaza Apartments</t>
+  </si>
+  <si>
     <t>Hob House</t>
   </si>
   <si>
-    <t>Kingfisher Nest Hotel Suites</t>
-  </si>
-  <si>
-    <t>Cloud Hotel &amp; Suites</t>
-  </si>
-  <si>
-    <t>Hotel Troy Nairobi</t>
-  </si>
-  <si>
-    <t>Diamond Plaza Apartments</t>
-  </si>
-  <si>
     <t>Mövenpick Hotel &amp; Residences Nairobi</t>
   </si>
   <si>
@@ -50,6 +50,9 @@
     <t>Best Western Premier Westlands</t>
   </si>
   <si>
+    <t>Trademark Hotel</t>
+  </si>
+  <si>
     <t>Best Western Plus Meridian Hotel</t>
   </si>
   <si>
@@ -105,9 +108,6 @@
   </si>
   <si>
     <t>Bidwood Suite Hotel</t>
-  </si>
-  <si>
-    <t>Executive Residency by Best Western Nairobi</t>
   </si>
 </sst>
 </file>
